--- a/tasks/finalpool/fetch-sf-hr-worklife-excel-word-gcal/groundtruth_workspace/Hr_Worklife_Report.xlsx
+++ b/tasks/finalpool/fetch-sf-hr-worklife-excel-word-gcal/groundtruth_workspace/Hr_Worklife_Report.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,30 +440,15 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Employee_Count</t>
+          <t>Our_Avg_Salary</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Our_Avg_Salary</t>
+          <t>Industry_Benchmark</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Avg_Experience</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Avg_Performance</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Industry_Benchmark</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Salary_Gap</t>
         </is>
@@ -476,21 +461,12 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7096</v>
+        <v>58991.61</v>
       </c>
       <c r="C2" t="n">
-        <v>58991.61</v>
+        <v>66816</v>
       </c>
       <c r="D2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="F2" t="n">
-        <v>66816</v>
-      </c>
-      <c r="G2" t="n">
         <v>-7824.39</v>
       </c>
     </row>
@@ -501,21 +477,12 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7148</v>
+        <v>57878.19</v>
       </c>
       <c r="C3" t="n">
-        <v>57878.19</v>
+        <v>79324</v>
       </c>
       <c r="D3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="F3" t="n">
-        <v>79324</v>
-      </c>
-      <c r="G3" t="n">
         <v>-21445.81</v>
       </c>
     </row>
@@ -526,21 +493,12 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7077</v>
+        <v>58920.45</v>
       </c>
       <c r="C4" t="n">
-        <v>58920.45</v>
+        <v>67899</v>
       </c>
       <c r="D4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>67899</v>
-      </c>
-      <c r="G4" t="n">
         <v>-8978.549999999999</v>
       </c>
     </row>
@@ -551,21 +509,12 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7120</v>
+        <v>57808.74</v>
       </c>
       <c r="C5" t="n">
-        <v>57808.74</v>
+        <v>72812</v>
       </c>
       <c r="D5" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="F5" t="n">
-        <v>72812</v>
-      </c>
-      <c r="G5" t="n">
         <v>-15003.26</v>
       </c>
     </row>
@@ -576,21 +525,12 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7083</v>
+        <v>57905.93</v>
       </c>
       <c r="C6" t="n">
-        <v>57905.93</v>
+        <v>74771</v>
       </c>
       <c r="D6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>74771</v>
-      </c>
-      <c r="G6" t="n">
         <v>-16865.07</v>
       </c>
     </row>
@@ -601,21 +541,12 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7232</v>
+        <v>58864.79</v>
       </c>
       <c r="C7" t="n">
-        <v>58864.79</v>
+        <v>77904</v>
       </c>
       <c r="D7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="F7" t="n">
-        <v>77904</v>
-      </c>
-      <c r="G7" t="n">
         <v>-19039.21</v>
       </c>
     </row>
@@ -626,21 +557,12 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7244</v>
+        <v>58400.48</v>
       </c>
       <c r="C8" t="n">
-        <v>58400.48</v>
+        <v>61709</v>
       </c>
       <c r="D8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>61709</v>
-      </c>
-      <c r="G8" t="n">
         <v>-3308.52</v>
       </c>
     </row>
@@ -731,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -750,11 +672,6 @@
           <t>Department</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,11 +687,6 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -790,11 +702,6 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -808,11 +715,6 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>Support</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Low</t>
         </is>
       </c>
     </row>
